--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,50 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788719</v>
+        <v>129788683</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -730,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472312</v>
+        <v>472158</v>
       </c>
       <c r="R2" t="n">
-        <v>7028922</v>
+        <v>7028919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,13 +771,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788683</v>
+        <v>129788693</v>
       </c>
       <c r="B3" t="n">
         <v>57736</v>
@@ -850,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472158</v>
+        <v>472086</v>
       </c>
       <c r="R3" t="n">
-        <v>7028919</v>
+        <v>7028965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -942,42 +953,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788693</v>
+        <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R4" t="n">
-        <v>7028965</v>
+        <v>7028922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1048,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,32 +1057,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,50 +1081,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788724</v>
+        <v>129788697</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1136,10 +1128,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472142</v>
+        <v>472086</v>
       </c>
       <c r="R5" t="n">
-        <v>7028942</v>
+        <v>7028958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,7 +1168,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,13 +1177,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,42 +1220,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788697</v>
+        <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1256,10 +1275,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472086</v>
+        <v>472142</v>
       </c>
       <c r="R6" t="n">
-        <v>7028958</v>
+        <v>7028942</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1296,7 +1315,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,32 +1324,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,50 +1348,42 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788721</v>
+        <v>129788698</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1403,10 +1395,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472388</v>
+        <v>472086</v>
       </c>
       <c r="R7" t="n">
-        <v>7028829</v>
+        <v>7028944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1443,7 +1435,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,13 +1444,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1476,7 +1487,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788698</v>
+        <v>129788692</v>
       </c>
       <c r="B8" t="n">
         <v>57736</v>
@@ -1509,7 +1520,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1523,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472086</v>
+        <v>472092</v>
       </c>
       <c r="R8" t="n">
-        <v>7028944</v>
+        <v>7028968</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1563,7 +1574,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1615,7 +1626,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788703</v>
+        <v>129788686</v>
       </c>
       <c r="B9" t="n">
         <v>57736</v>
@@ -1648,7 +1659,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1662,10 +1673,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472087</v>
+        <v>472112</v>
       </c>
       <c r="R9" t="n">
-        <v>7028909</v>
+        <v>7028955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,7 +1713,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,7 +1727,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1754,7 +1765,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788692</v>
+        <v>129788704</v>
       </c>
       <c r="B10" t="n">
         <v>57736</v>
@@ -1801,10 +1812,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472092</v>
+        <v>472090</v>
       </c>
       <c r="R10" t="n">
-        <v>7028968</v>
+        <v>7028888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1855,7 +1866,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1893,45 +1904,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788707</v>
+        <v>129788703</v>
       </c>
       <c r="B11" t="n">
-        <v>97645</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472260</v>
+        <v>472087</v>
       </c>
       <c r="R11" t="n">
-        <v>7028803</v>
+        <v>7028909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1966,6 +1989,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1974,6 +2002,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1990,65 +2043,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788716</v>
+        <v>129788707</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472440</v>
+        <v>472260</v>
       </c>
       <c r="R12" t="n">
-        <v>7028732</v>
+        <v>7028803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,25 +2116,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2118,42 +2140,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788686</v>
+        <v>129788716</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2165,10 +2195,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472112</v>
+        <v>472440</v>
       </c>
       <c r="R13" t="n">
-        <v>7028955</v>
+        <v>7028732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2205,7 +2235,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2214,32 +2244,13 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2257,42 +2268,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788704</v>
+        <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2304,10 +2323,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472090</v>
+        <v>472388</v>
       </c>
       <c r="R14" t="n">
-        <v>7028888</v>
+        <v>7028829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,7 +2363,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2353,32 +2372,13 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129788687</v>
+        <v>129788702</v>
       </c>
       <c r="B15" t="n">
         <v>57736</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472094</v>
+        <v>472087</v>
       </c>
       <c r="R15" t="n">
-        <v>7029010</v>
+        <v>7028916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2535,7 +2535,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129788702</v>
+        <v>129788687</v>
       </c>
       <c r="B16" t="n">
         <v>57736</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472087</v>
+        <v>472094</v>
       </c>
       <c r="R16" t="n">
-        <v>7028916</v>
+        <v>7029010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2674,50 +2674,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788720</v>
+        <v>129788688</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2729,10 +2721,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472282</v>
+        <v>472089</v>
       </c>
       <c r="R17" t="n">
-        <v>7028952</v>
+        <v>7029005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2769,7 +2761,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2778,13 +2770,32 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2802,7 +2813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2835,7 +2846,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2849,10 +2860,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R18" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2903,7 +2914,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3064,57 +3075,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788705</v>
+        <v>129788706</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472092</v>
+        <v>472382</v>
       </c>
       <c r="R20" t="n">
-        <v>7028874</v>
+        <v>7028711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3151,7 +3150,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3162,31 +3161,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3203,7 +3177,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788714</v>
+        <v>129788720</v>
       </c>
       <c r="B21" t="n">
         <v>98774</v>
@@ -3233,7 +3207,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3258,10 +3232,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472482</v>
+        <v>472282</v>
       </c>
       <c r="R21" t="n">
-        <v>7028718</v>
+        <v>7028952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3298,7 +3272,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,7 +3287,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B22" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4390,50 +4390,42 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788723</v>
+        <v>129788701</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4445,7 +4437,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472131</v>
+        <v>472090</v>
       </c>
       <c r="R30" t="n">
         <v>7028919</v>
@@ -4485,7 +4477,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4494,13 +4486,32 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4518,42 +4529,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788701</v>
+        <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4565,7 +4584,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472090</v>
+        <v>472131</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4605,7 +4624,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4614,32 +4633,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4657,65 +4657,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788722</v>
+        <v>129788672</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472240</v>
+        <v>472381</v>
       </c>
       <c r="R32" t="n">
-        <v>7028927</v>
+        <v>7028719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,7 +4739,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4767,7 +4754,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4785,10 +4792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788672</v>
+        <v>129788699</v>
       </c>
       <c r="B33" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4796,41 +4803,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472381</v>
+        <v>472089</v>
       </c>
       <c r="R33" t="n">
-        <v>7028719</v>
+        <v>7028934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4867,7 +4879,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,7 +4888,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4897,12 +4908,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4920,7 +4931,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788699</v>
+        <v>129788682</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4967,10 +4978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472089</v>
+        <v>472181</v>
       </c>
       <c r="R34" t="n">
-        <v>7028934</v>
+        <v>7028935</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5007,7 +5018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5059,42 +5070,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788682</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5106,10 +5125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472181</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028935</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5155,32 +5174,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5198,65 +5198,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788715</v>
+        <v>129788727</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472454</v>
+        <v>472319</v>
       </c>
       <c r="R36" t="n">
-        <v>7028715</v>
+        <v>7028798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5293,7 +5276,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5309,6 +5292,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5326,10 +5329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788689</v>
+        <v>129788673</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5337,46 +5340,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472086</v>
+        <v>472242</v>
       </c>
       <c r="R37" t="n">
-        <v>7028991</v>
+        <v>7028816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5413,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5422,12 +5420,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5442,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5465,10 +5464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788727</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5476,37 +5475,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472319</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028798</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5543,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5552,13 +5560,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5573,12 +5580,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5874,52 +5881,65 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788673</v>
+        <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472242</v>
+        <v>472454</v>
       </c>
       <c r="R41" t="n">
-        <v>7028816</v>
+        <v>7028715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5956,7 +5976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5972,26 +5992,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,50 +6009,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788718</v>
+        <v>129788684</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6064,10 +6056,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472399</v>
+        <v>472106</v>
       </c>
       <c r="R42" t="n">
-        <v>7028764</v>
+        <v>7028852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6096,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6113,13 +6105,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6265,42 +6276,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788684</v>
+        <v>129788718</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6312,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472106</v>
+        <v>472399</v>
       </c>
       <c r="R44" t="n">
-        <v>7028852</v>
+        <v>7028764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6352,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6361,32 +6380,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -2043,45 +2043,65 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788707</v>
+        <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472260</v>
+        <v>472440</v>
       </c>
       <c r="R12" t="n">
-        <v>7028803</v>
+        <v>7028732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,14 +2136,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2140,7 +2171,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788716</v>
+        <v>129788721</v>
       </c>
       <c r="B13" t="n">
         <v>98774</v>
@@ -2170,7 +2201,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2195,10 +2226,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472440</v>
+        <v>472388</v>
       </c>
       <c r="R13" t="n">
-        <v>7028732</v>
+        <v>7028829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2235,7 +2266,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,7 +2281,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2268,65 +2299,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R14" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,25 +2372,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2674,57 +2674,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788688</v>
+        <v>129788706</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472089</v>
+        <v>472382</v>
       </c>
       <c r="R17" t="n">
-        <v>7029005</v>
+        <v>7028711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,7 +2749,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,31 +2760,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2813,7 +2776,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2846,7 +2809,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2860,10 +2823,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R18" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2900,7 +2863,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2914,7 +2877,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2952,27 +2915,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788709</v>
+        <v>129788705</v>
       </c>
       <c r="B19" t="n">
-        <v>58106</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2980,16 +2943,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3003,10 +2962,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472246</v>
+        <v>472092</v>
       </c>
       <c r="R19" t="n">
-        <v>7028867</v>
+        <v>7028874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3043,7 +3002,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3057,7 +3016,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3075,10 +3054,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788706</v>
+        <v>129788709</v>
       </c>
       <c r="B20" t="n">
-        <v>97645</v>
+        <v>58106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3086,34 +3065,50 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472382</v>
+        <v>472246</v>
       </c>
       <c r="R20" t="n">
-        <v>7028711</v>
+        <v>7028867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3150,7 +3145,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3161,6 +3156,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -6009,42 +6009,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788684</v>
+        <v>129788713</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6056,10 +6064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472106</v>
+        <v>472513</v>
       </c>
       <c r="R42" t="n">
-        <v>7028852</v>
+        <v>7028648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6096,7 +6104,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6105,32 +6113,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,7 +6137,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B43" t="n">
         <v>98774</v>
@@ -6178,7 +6167,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6232,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6258,7 +6247,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,50 +6265,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788718</v>
+        <v>129788684</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6331,10 +6312,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472399</v>
+        <v>472106</v>
       </c>
       <c r="R44" t="n">
-        <v>7028764</v>
+        <v>7028852</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6352,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6380,13 +6361,32 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,42 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788719</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -722,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472312</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,32 +779,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788683</v>
       </c>
       <c r="B3" t="n">
         <v>57736</v>
@@ -861,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472158</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +904,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -953,50 +942,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788693</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472086</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,13 +1038,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -2674,10 +2674,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788706</v>
+        <v>129788709</v>
       </c>
       <c r="B17" t="n">
-        <v>97645</v>
+        <v>58106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2685,34 +2685,50 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472382</v>
+        <v>472246</v>
       </c>
       <c r="R17" t="n">
-        <v>7028711</v>
+        <v>7028867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2765,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2760,6 +2776,11 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2776,42 +2797,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788688</v>
+        <v>129788720</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2823,10 +2852,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472089</v>
+        <v>472282</v>
       </c>
       <c r="R18" t="n">
-        <v>7029005</v>
+        <v>7028952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2863,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2872,32 +2901,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2915,57 +2925,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788705</v>
+        <v>129788706</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>97645</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472092</v>
+        <v>472382</v>
       </c>
       <c r="R19" t="n">
-        <v>7028874</v>
+        <v>7028711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3002,7 +3000,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3013,31 +3011,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3054,46 +3027,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788709</v>
+        <v>129788714</v>
       </c>
       <c r="B20" t="n">
-        <v>58106</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3105,10 +3082,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472246</v>
+        <v>472482</v>
       </c>
       <c r="R20" t="n">
-        <v>7028867</v>
+        <v>7028718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3145,7 +3122,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3154,12 +3131,13 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3177,50 +3155,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788720</v>
+        <v>129788688</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3232,10 +3202,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472282</v>
+        <v>472089</v>
       </c>
       <c r="R21" t="n">
-        <v>7028952</v>
+        <v>7029005</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3272,7 +3242,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3281,13 +3251,32 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3305,50 +3294,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788714</v>
+        <v>129788705</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3360,10 +3341,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472482</v>
+        <v>472092</v>
       </c>
       <c r="R22" t="n">
-        <v>7028718</v>
+        <v>7028874</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3381,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,13 +3390,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B27" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R27" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R28" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -5198,48 +5198,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788727</v>
+        <v>129788715</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472319</v>
+        <v>472454</v>
       </c>
       <c r="R36" t="n">
-        <v>7028798</v>
+        <v>7028715</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5276,7 +5293,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5292,26 +5309,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5464,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788727</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5475,46 +5472,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472319</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5539,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,12 +5548,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5580,12 +5569,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5603,7 +5592,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788689</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5636,7 +5625,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5650,10 +5639,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472086</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5679,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,7 +5731,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788690</v>
       </c>
       <c r="B40" t="n">
         <v>57736</v>
@@ -5775,7 +5764,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5789,10 +5778,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472088</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028985</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5818,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5881,50 +5870,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788715</v>
+        <v>129788700</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5936,10 +5917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472454</v>
+        <v>472091</v>
       </c>
       <c r="R41" t="n">
-        <v>7028715</v>
+        <v>7028924</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,7 +5957,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5985,13 +5966,32 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B42" t="n">
         <v>98774</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R42" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B43" t="n">
         <v>98774</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R43" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,50 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788719</v>
+        <v>129788683</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -730,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472312</v>
+        <v>472158</v>
       </c>
       <c r="R2" t="n">
-        <v>7028922</v>
+        <v>7028919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,13 +771,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788683</v>
+        <v>129788693</v>
       </c>
       <c r="B3" t="n">
         <v>57736</v>
@@ -850,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472158</v>
+        <v>472086</v>
       </c>
       <c r="R3" t="n">
-        <v>7028919</v>
+        <v>7028965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -942,42 +953,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788693</v>
+        <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R4" t="n">
-        <v>7028965</v>
+        <v>7028922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1048,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,32 +1057,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,42 +1081,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788697</v>
+        <v>129788724</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1128,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472086</v>
+        <v>472142</v>
       </c>
       <c r="R5" t="n">
-        <v>7028958</v>
+        <v>7028942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,32 +1185,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,50 +1209,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788724</v>
+        <v>129788697</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1275,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472142</v>
+        <v>472086</v>
       </c>
       <c r="R6" t="n">
-        <v>7028942</v>
+        <v>7028958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,7 +1296,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,13 +1305,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2797,65 +2797,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788720</v>
+        <v>129788706</v>
       </c>
       <c r="B18" t="n">
-        <v>98774</v>
+        <v>97645</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472282</v>
+        <v>472382</v>
       </c>
       <c r="R18" t="n">
-        <v>7028952</v>
+        <v>7028711</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2872,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2901,14 +2881,8 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2925,45 +2899,65 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788706</v>
+        <v>129788720</v>
       </c>
       <c r="B19" t="n">
-        <v>97645</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472382</v>
+        <v>472282</v>
       </c>
       <c r="R19" t="n">
-        <v>7028711</v>
+        <v>7028952</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3000,7 +2994,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3009,8 +3003,14 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91613</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>91613</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4251,42 +4251,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788694</v>
+        <v>129788723</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4298,10 +4306,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472085</v>
+        <v>472131</v>
       </c>
       <c r="R29" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4347,32 +4355,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4390,7 +4379,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788701</v>
+        <v>129788694</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -4423,7 +4412,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4437,10 +4426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472090</v>
+        <v>472085</v>
       </c>
       <c r="R30" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4477,7 +4466,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4529,50 +4518,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788723</v>
+        <v>129788701</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4584,7 +4565,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472131</v>
+        <v>472090</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4624,7 +4605,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4633,13 +4614,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4657,52 +4657,65 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788672</v>
+        <v>129788722</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472381</v>
+        <v>472240</v>
       </c>
       <c r="R32" t="n">
-        <v>7028719</v>
+        <v>7028927</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4739,7 +4752,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4754,27 +4767,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -5070,65 +5063,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788672</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472381</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028719</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5180,7 +5160,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5198,65 +5198,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788715</v>
+        <v>129788673</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472454</v>
+        <v>472242</v>
       </c>
       <c r="R36" t="n">
-        <v>7028715</v>
+        <v>7028816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5293,7 +5280,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5309,6 +5296,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5326,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788673</v>
+        <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5337,30 +5344,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5368,10 +5371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472242</v>
+        <v>472319</v>
       </c>
       <c r="R37" t="n">
-        <v>7028816</v>
+        <v>7028798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5408,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5438,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5461,10 +5464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788727</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5472,37 +5475,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472319</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028798</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5539,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5548,13 +5560,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5569,12 +5580,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5592,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788689</v>
+        <v>129788690</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5625,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5639,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472086</v>
+        <v>472088</v>
       </c>
       <c r="R39" t="n">
-        <v>7028991</v>
+        <v>7028985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5679,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5731,7 +5742,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788690</v>
+        <v>129788700</v>
       </c>
       <c r="B40" t="n">
         <v>57736</v>
@@ -5764,7 +5775,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5778,10 +5789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472088</v>
+        <v>472091</v>
       </c>
       <c r="R40" t="n">
-        <v>7028985</v>
+        <v>7028924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5818,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5870,42 +5881,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788700</v>
+        <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5917,10 +5936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472091</v>
+        <v>472454</v>
       </c>
       <c r="R41" t="n">
-        <v>7028924</v>
+        <v>7028715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5957,7 +5976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5966,32 +5985,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B42" t="n">
         <v>98774</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R42" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6137,7 +6137,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B43" t="n">
         <v>98774</v>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,50 +1081,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788724</v>
+        <v>129788697</v>
       </c>
       <c r="B5" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1136,10 +1128,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472142</v>
+        <v>472086</v>
       </c>
       <c r="R5" t="n">
-        <v>7028942</v>
+        <v>7028958</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1176,7 +1168,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,13 +1177,32 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1209,42 +1220,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788697</v>
+        <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1256,10 +1275,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472086</v>
+        <v>472142</v>
       </c>
       <c r="R6" t="n">
-        <v>7028958</v>
+        <v>7028942</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1296,7 +1315,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,32 +1324,13 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2046,7 +2046,7 @@
         <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>129788721</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>97645</v>
+        <v>97649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2674,27 +2674,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788709</v>
+        <v>129788688</v>
       </c>
       <c r="B17" t="n">
-        <v>58106</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2702,16 +2702,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2725,10 +2721,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472246</v>
+        <v>472089</v>
       </c>
       <c r="R17" t="n">
-        <v>7028867</v>
+        <v>7029005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2765,7 +2761,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2780,6 +2776,26 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2797,45 +2813,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788706</v>
+        <v>129788705</v>
       </c>
       <c r="B18" t="n">
-        <v>97645</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472382</v>
+        <v>472092</v>
       </c>
       <c r="R18" t="n">
-        <v>7028711</v>
+        <v>7028874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2872,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2883,6 +2911,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2902,7 +2955,7 @@
         <v>129788720</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3030,7 +3083,7 @@
         <v>129788714</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3155,27 +3208,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788688</v>
+        <v>129788709</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>58106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3183,12 +3236,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3202,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472089</v>
+        <v>472246</v>
       </c>
       <c r="R21" t="n">
-        <v>7029005</v>
+        <v>7028867</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3242,7 +3299,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3257,26 +3314,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3294,57 +3331,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788705</v>
+        <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>97649</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472092</v>
+        <v>472382</v>
       </c>
       <c r="R22" t="n">
-        <v>7028874</v>
+        <v>7028711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3381,7 +3406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3392,31 +3417,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3992,7 +3992,7 @@
         <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>129788723</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4657,50 +4657,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4712,10 +4704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R32" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4761,13 +4753,32 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4785,10 +4796,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788699</v>
+        <v>129788672</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4796,46 +4807,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472089</v>
+        <v>472381</v>
       </c>
       <c r="R33" t="n">
-        <v>7028934</v>
+        <v>7028719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4872,7 +4878,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4881,6 +4887,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4901,12 +4908,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4924,7 +4931,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4971,10 +4978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R34" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5011,7 +5018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5063,52 +5070,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788672</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472381</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028719</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5145,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5160,27 +5180,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788673</v>
+        <v>129788727</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5209,30 +5209,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5240,10 +5236,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472242</v>
+        <v>472319</v>
       </c>
       <c r="R36" t="n">
-        <v>7028816</v>
+        <v>7028798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5280,7 +5276,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5310,12 +5306,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5333,10 +5329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788727</v>
+        <v>129788673</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,26 +5340,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472319</v>
+        <v>472242</v>
       </c>
       <c r="R37" t="n">
-        <v>7028798</v>
+        <v>7028816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
         <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>129788713</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>129788718</v>
       </c>
       <c r="B43" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2171,65 +2171,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>97651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R13" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2264,25 +2244,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2299,45 +2268,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788707</v>
+        <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>97649</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472260</v>
+        <v>472388</v>
       </c>
       <c r="R14" t="n">
-        <v>7028803</v>
+        <v>7028829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2372,14 +2361,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2674,57 +2674,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788688</v>
+        <v>129788706</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>97651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472089</v>
+        <v>472382</v>
       </c>
       <c r="R17" t="n">
-        <v>7029005</v>
+        <v>7028711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,7 +2749,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,31 +2760,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2813,7 +2776,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2846,7 +2809,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2860,10 +2823,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R18" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2900,7 +2863,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2914,7 +2877,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2952,50 +2915,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788720</v>
+        <v>129788705</v>
       </c>
       <c r="B19" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3007,10 +2962,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472282</v>
+        <v>472092</v>
       </c>
       <c r="R19" t="n">
-        <v>7028952</v>
+        <v>7028874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3047,7 +3002,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3056,13 +3011,32 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,50 +3054,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788714</v>
+        <v>129788709</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>58106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3135,10 +3105,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472482</v>
+        <v>472246</v>
       </c>
       <c r="R20" t="n">
-        <v>7028718</v>
+        <v>7028867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3175,7 +3145,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3184,13 +3154,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3208,46 +3177,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788709</v>
+        <v>129788720</v>
       </c>
       <c r="B21" t="n">
-        <v>58106</v>
+        <v>98780</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3259,10 +3232,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472246</v>
+        <v>472282</v>
       </c>
       <c r="R21" t="n">
-        <v>7028867</v>
+        <v>7028952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3299,7 +3272,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3308,6 +3281,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B22" t="n">
-        <v>97649</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3992,7 +3992,7 @@
         <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4251,50 +4251,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788723</v>
+        <v>129788694</v>
       </c>
       <c r="B29" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4306,10 +4298,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472131</v>
+        <v>472085</v>
       </c>
       <c r="R29" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4346,7 +4338,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4355,13 +4347,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4379,7 +4390,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788694</v>
+        <v>129788701</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -4412,7 +4423,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4426,10 +4437,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472085</v>
+        <v>472090</v>
       </c>
       <c r="R30" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4466,7 +4477,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4518,42 +4529,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788701</v>
+        <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4565,7 +4584,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472090</v>
+        <v>472131</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4605,7 +4624,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4614,32 +4633,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4657,42 +4657,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788682</v>
+        <v>129788722</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4704,10 +4712,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472181</v>
+        <v>472240</v>
       </c>
       <c r="R32" t="n">
-        <v>7028935</v>
+        <v>7028927</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4752,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4753,32 +4761,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4799,7 +4788,7 @@
         <v>129788672</v>
       </c>
       <c r="B33" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5070,50 +5059,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B35" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5125,10 +5106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5146,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5174,13 +5155,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5332,7 +5332,7 @@
         <v>129788673</v>
       </c>
       <c r="B37" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6009,50 +6009,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788713</v>
+        <v>129788684</v>
       </c>
       <c r="B42" t="n">
-        <v>98778</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6064,10 +6056,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472513</v>
+        <v>472106</v>
       </c>
       <c r="R42" t="n">
-        <v>7028648</v>
+        <v>7028852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6096,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6113,13 +6105,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6137,10 +6148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B43" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6167,7 +6178,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6192,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R43" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6232,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6247,7 +6258,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6265,42 +6276,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788684</v>
+        <v>129788718</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6312,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472106</v>
+        <v>472399</v>
       </c>
       <c r="R44" t="n">
-        <v>7028852</v>
+        <v>7028764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6352,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6361,32 +6380,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -2043,7 +2043,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788716</v>
+        <v>129788721</v>
       </c>
       <c r="B12" t="n">
         <v>98780</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472440</v>
+        <v>472388</v>
       </c>
       <c r="R12" t="n">
-        <v>7028732</v>
+        <v>7028829</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2171,45 +2171,65 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788707</v>
+        <v>129788716</v>
       </c>
       <c r="B13" t="n">
-        <v>97651</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472260</v>
+        <v>472440</v>
       </c>
       <c r="R13" t="n">
-        <v>7028803</v>
+        <v>7028732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2244,14 +2264,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2268,65 +2299,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>97651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R14" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,25 +2372,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -5198,10 +5198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788727</v>
+        <v>129788673</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5209,26 +5209,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5236,10 +5240,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472319</v>
+        <v>472242</v>
       </c>
       <c r="R36" t="n">
-        <v>7028798</v>
+        <v>7028816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5276,7 +5280,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5306,12 +5310,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5329,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788673</v>
+        <v>129788689</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5340,41 +5344,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472242</v>
+        <v>472086</v>
       </c>
       <c r="R37" t="n">
-        <v>7028816</v>
+        <v>7028991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5420,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5420,13 +5429,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5441,12 +5449,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5464,7 +5472,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788690</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -5497,7 +5505,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5511,10 +5519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472088</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028985</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5559,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5603,7 +5611,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788700</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5636,7 +5644,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5650,10 +5658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472091</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028924</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5698,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,42 +5750,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788715</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5789,10 +5805,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472454</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028715</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5845,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5838,32 +5854,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5881,65 +5878,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788715</v>
+        <v>129788727</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472454</v>
+        <v>472319</v>
       </c>
       <c r="R41" t="n">
-        <v>7028715</v>
+        <v>7028798</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,7 +5956,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5992,6 +5972,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -2674,45 +2674,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788706</v>
+        <v>129788688</v>
       </c>
       <c r="B17" t="n">
-        <v>97651</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472382</v>
+        <v>472089</v>
       </c>
       <c r="R17" t="n">
-        <v>7028711</v>
+        <v>7029005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2761,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2760,6 +2772,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2776,7 +2813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B18" t="n">
         <v>57736</v>
@@ -2809,7 +2846,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2823,10 +2860,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R18" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2863,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2877,7 +2914,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2915,27 +2952,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788705</v>
+        <v>129788709</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>58106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2943,12 +2980,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2962,10 +3003,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472092</v>
+        <v>472246</v>
       </c>
       <c r="R19" t="n">
-        <v>7028874</v>
+        <v>7028867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3002,7 +3043,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3016,27 +3057,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3054,46 +3075,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788709</v>
+        <v>129788720</v>
       </c>
       <c r="B20" t="n">
-        <v>58106</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3105,10 +3130,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472246</v>
+        <v>472282</v>
       </c>
       <c r="R20" t="n">
-        <v>7028867</v>
+        <v>7028952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3145,7 +3170,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3154,6 +3179,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3177,7 +3203,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788720</v>
+        <v>129788714</v>
       </c>
       <c r="B21" t="n">
         <v>98780</v>
@@ -3207,7 +3233,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3232,10 +3258,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472282</v>
+        <v>472482</v>
       </c>
       <c r="R21" t="n">
-        <v>7028952</v>
+        <v>7028718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3272,7 +3298,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3287,7 +3313,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3305,65 +3331,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788714</v>
+        <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>97651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472482</v>
+        <v>472382</v>
       </c>
       <c r="R22" t="n">
-        <v>7028718</v>
+        <v>7028711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,14 +3415,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4657,50 +4657,42 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788722</v>
+        <v>129788699</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4712,10 +4704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472240</v>
+        <v>472089</v>
       </c>
       <c r="R32" t="n">
-        <v>7028927</v>
+        <v>7028934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4761,13 +4753,32 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4785,10 +4796,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788672</v>
+        <v>129788682</v>
       </c>
       <c r="B33" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4796,41 +4807,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472381</v>
+        <v>472181</v>
       </c>
       <c r="R33" t="n">
-        <v>7028719</v>
+        <v>7028935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4867,7 +4883,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,7 +4892,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4897,12 +4912,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4920,10 +4935,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788699</v>
+        <v>129788672</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4931,46 +4946,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472089</v>
+        <v>472381</v>
       </c>
       <c r="R34" t="n">
-        <v>7028934</v>
+        <v>7028719</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5007,7 +5017,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5016,6 +5026,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5036,12 +5047,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5059,42 +5070,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788682</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5106,10 +5125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472181</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028935</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5155,32 +5174,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -4657,42 +4657,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788699</v>
+        <v>129788722</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4704,10 +4712,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472089</v>
+        <v>472240</v>
       </c>
       <c r="R32" t="n">
-        <v>7028934</v>
+        <v>7028927</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4752,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4753,32 +4761,13 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4796,10 +4785,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788682</v>
+        <v>129788672</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4807,46 +4796,41 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472181</v>
+        <v>472381</v>
       </c>
       <c r="R33" t="n">
-        <v>7028935</v>
+        <v>7028719</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4883,7 +4867,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4892,6 +4876,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4912,12 +4897,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4935,10 +4920,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788672</v>
+        <v>129788699</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4946,41 +4931,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472381</v>
+        <v>472089</v>
       </c>
       <c r="R34" t="n">
-        <v>7028719</v>
+        <v>7028934</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5017,7 +5007,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5026,7 +5016,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5047,12 +5036,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5070,50 +5059,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5125,10 +5106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5146,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5174,13 +5155,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,42 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788719</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -722,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472312</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,32 +779,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788683</v>
       </c>
       <c r="B3" t="n">
         <v>57736</v>
@@ -861,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472158</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +904,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -953,50 +942,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788693</v>
       </c>
       <c r="B4" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472086</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,13 +1038,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
         <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2043,65 +2043,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>97661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R12" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2136,25 +2116,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2174,7 +2143,7 @@
         <v>129788716</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2299,45 +2268,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788707</v>
+        <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>97651</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472260</v>
+        <v>472388</v>
       </c>
       <c r="R14" t="n">
-        <v>7028803</v>
+        <v>7028829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2372,14 +2361,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788709</v>
+        <v>129788706</v>
       </c>
       <c r="B19" t="n">
-        <v>58106</v>
+        <v>97661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2963,50 +2963,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472246</v>
+        <v>472382</v>
       </c>
       <c r="R19" t="n">
-        <v>7028867</v>
+        <v>7028711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3043,7 +3027,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3054,11 +3038,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3075,50 +3054,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788720</v>
+        <v>129788709</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>58106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3130,10 +3105,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472282</v>
+        <v>472246</v>
       </c>
       <c r="R20" t="n">
-        <v>7028952</v>
+        <v>7028867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3170,7 +3145,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3179,7 +3154,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3203,10 +3177,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788714</v>
+        <v>129788720</v>
       </c>
       <c r="B21" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3233,7 +3207,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3258,10 +3232,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472482</v>
+        <v>472282</v>
       </c>
       <c r="R21" t="n">
-        <v>7028718</v>
+        <v>7028952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3298,7 +3272,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,7 +3287,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B22" t="n">
-        <v>97651</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4532,7 +4532,7 @@
         <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4657,65 +4657,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788722</v>
+        <v>129788672</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472240</v>
+        <v>472381</v>
       </c>
       <c r="R32" t="n">
-        <v>7028927</v>
+        <v>7028719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4752,7 +4739,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4767,7 +4754,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4785,10 +4792,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788672</v>
+        <v>129788699</v>
       </c>
       <c r="B33" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4796,41 +4803,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472381</v>
+        <v>472089</v>
       </c>
       <c r="R33" t="n">
-        <v>7028719</v>
+        <v>7028934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4867,7 +4879,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4876,7 +4888,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4897,12 +4908,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4920,7 +4931,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788699</v>
+        <v>129788682</v>
       </c>
       <c r="B34" t="n">
         <v>57736</v>
@@ -4967,10 +4978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472089</v>
+        <v>472181</v>
       </c>
       <c r="R34" t="n">
-        <v>7028934</v>
+        <v>7028935</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5007,7 +5018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5059,42 +5070,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788682</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5106,10 +5125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472181</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028935</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5155,32 +5174,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5750,65 +5750,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788715</v>
+        <v>129788727</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472454</v>
+        <v>472319</v>
       </c>
       <c r="R40" t="n">
-        <v>7028715</v>
+        <v>7028798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5845,7 +5828,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5861,6 +5844,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5878,48 +5881,65 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788727</v>
+        <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472319</v>
+        <v>472454</v>
       </c>
       <c r="R41" t="n">
-        <v>7028798</v>
+        <v>7028715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5956,7 +5976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5972,26 +5992,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,42 +6009,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788684</v>
+        <v>129788713</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6056,10 +6064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472106</v>
+        <v>472513</v>
       </c>
       <c r="R42" t="n">
-        <v>7028852</v>
+        <v>7028648</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6096,7 +6104,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6105,32 +6113,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,10 +6137,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B43" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6178,7 +6167,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6192,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6232,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6258,7 +6247,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,50 +6265,42 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788718</v>
+        <v>129788684</v>
       </c>
       <c r="B44" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6331,10 +6312,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472399</v>
+        <v>472106</v>
       </c>
       <c r="R44" t="n">
-        <v>7028764</v>
+        <v>7028852</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6352,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6380,13 +6361,32 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -2043,45 +2043,65 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788707</v>
+        <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>97661</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472260</v>
+        <v>472440</v>
       </c>
       <c r="R12" t="n">
-        <v>7028803</v>
+        <v>7028732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,14 +2136,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2140,7 +2171,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788716</v>
+        <v>129788721</v>
       </c>
       <c r="B13" t="n">
         <v>98790</v>
@@ -2170,7 +2201,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2195,10 +2226,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472440</v>
+        <v>472388</v>
       </c>
       <c r="R13" t="n">
-        <v>7028732</v>
+        <v>7028829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2235,7 +2266,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,7 +2281,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2268,65 +2299,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>97661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R14" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,25 +2372,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2952,10 +2952,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788706</v>
+        <v>129788709</v>
       </c>
       <c r="B19" t="n">
-        <v>97661</v>
+        <v>58106</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2963,34 +2963,50 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472382</v>
+        <v>472246</v>
       </c>
       <c r="R19" t="n">
-        <v>7028711</v>
+        <v>7028867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3027,7 +3043,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3038,6 +3054,11 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3054,46 +3075,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788709</v>
+        <v>129788720</v>
       </c>
       <c r="B20" t="n">
-        <v>58106</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3105,10 +3130,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472246</v>
+        <v>472282</v>
       </c>
       <c r="R20" t="n">
-        <v>7028867</v>
+        <v>7028952</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3145,7 +3170,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3154,6 +3179,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3177,7 +3203,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788720</v>
+        <v>129788714</v>
       </c>
       <c r="B21" t="n">
         <v>98790</v>
@@ -3207,7 +3233,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3232,10 +3258,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472282</v>
+        <v>472482</v>
       </c>
       <c r="R21" t="n">
-        <v>7028952</v>
+        <v>7028718</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3272,7 +3298,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3287,7 +3313,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3305,65 +3331,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788714</v>
+        <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>97661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472482</v>
+        <v>472382</v>
       </c>
       <c r="R22" t="n">
-        <v>7028718</v>
+        <v>7028711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,14 +3415,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4251,42 +4251,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788694</v>
+        <v>129788723</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4298,10 +4306,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472085</v>
+        <v>472131</v>
       </c>
       <c r="R29" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4347,32 +4355,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4390,7 +4379,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788701</v>
+        <v>129788694</v>
       </c>
       <c r="B30" t="n">
         <v>57736</v>
@@ -4423,7 +4412,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4437,10 +4426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472090</v>
+        <v>472085</v>
       </c>
       <c r="R30" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4477,7 +4466,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4529,50 +4518,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788723</v>
+        <v>129788701</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4584,7 +4565,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472131</v>
+        <v>472090</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4624,7 +4605,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4633,13 +4614,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788689</v>
+        <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,46 +5344,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472086</v>
+        <v>472319</v>
       </c>
       <c r="R37" t="n">
-        <v>7028991</v>
+        <v>7028798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5420,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5429,12 +5420,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5449,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5472,7 +5464,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788690</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
         <v>57736</v>
@@ -5505,7 +5497,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5519,10 +5511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472088</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028985</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5559,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5611,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788700</v>
+        <v>129788690</v>
       </c>
       <c r="B39" t="n">
         <v>57736</v>
@@ -5644,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5658,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472091</v>
+        <v>472088</v>
       </c>
       <c r="R39" t="n">
-        <v>7028924</v>
+        <v>7028985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5698,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5750,10 +5742,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788727</v>
+        <v>129788700</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5761,37 +5753,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472319</v>
+        <v>472091</v>
       </c>
       <c r="R40" t="n">
-        <v>7028798</v>
+        <v>7028924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5828,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5837,13 +5838,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,50 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788719</v>
+        <v>129788683</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -730,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472312</v>
+        <v>472158</v>
       </c>
       <c r="R2" t="n">
-        <v>7028922</v>
+        <v>7028919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,13 +771,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788683</v>
+        <v>129788693</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472158</v>
+        <v>472086</v>
       </c>
       <c r="R3" t="n">
-        <v>7028919</v>
+        <v>7028965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -942,42 +953,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788693</v>
+        <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R4" t="n">
-        <v>7028965</v>
+        <v>7028922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1048,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,32 +1057,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
         <v>129788697</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>129788698</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>129788692</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>129788686</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>129788704</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>129788703</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>129788721</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>129788702</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>129788687</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>129788688</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>129788705</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129788709</v>
       </c>
       <c r="B19" t="n">
-        <v>58106</v>
+        <v>58108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         <v>129788720</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         <v>129788714</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>97661</v>
+        <v>97665</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>129788691</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129788685</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>129788681</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>129788696</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B27" t="n">
-        <v>91619</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R27" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>91622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R28" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4251,50 +4251,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788723</v>
+        <v>129788694</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4306,10 +4298,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472131</v>
+        <v>472085</v>
       </c>
       <c r="R29" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4346,7 +4338,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4355,13 +4347,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4379,10 +4390,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788694</v>
+        <v>129788701</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4412,7 +4423,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4426,10 +4437,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472085</v>
+        <v>472090</v>
       </c>
       <c r="R30" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4466,7 +4477,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4518,42 +4529,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788701</v>
+        <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4565,7 +4584,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472090</v>
+        <v>472131</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4605,7 +4624,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4614,32 +4633,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4660,7 +4660,7 @@
         <v>129788672</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>129788699</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>129788682</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5073,7 +5073,7 @@
         <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>129788673</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788727</v>
+        <v>129788689</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,37 +5344,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472319</v>
+        <v>472086</v>
       </c>
       <c r="R37" t="n">
-        <v>7028798</v>
+        <v>7028991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5420,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5420,13 +5429,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5441,12 +5449,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5464,10 +5472,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788690</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5497,7 +5505,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5511,10 +5519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472088</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028985</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5559,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5603,10 +5611,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788700</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5636,7 +5644,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5650,10 +5658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472091</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028924</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5698,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,10 +5750,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788727</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5753,46 +5761,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472319</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5828,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5838,12 +5837,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5884,7 +5884,7 @@
         <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6009,50 +6009,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788713</v>
+        <v>129788684</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6064,10 +6056,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472513</v>
+        <v>472106</v>
       </c>
       <c r="R42" t="n">
-        <v>7028648</v>
+        <v>7028852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6096,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6113,13 +6105,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6137,10 +6148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B43" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6167,7 +6178,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6192,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R43" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6232,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6247,7 +6258,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6265,42 +6276,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788684</v>
+        <v>129788718</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>98794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6312,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472106</v>
+        <v>472399</v>
       </c>
       <c r="R44" t="n">
-        <v>7028852</v>
+        <v>7028764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6352,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6361,32 +6380,13 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6407,7 +6407,7 @@
         <v>129788695</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788693</v>
       </c>
       <c r="B2" t="n">
         <v>57737</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472086</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +776,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -814,42 +814,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788719</v>
       </c>
       <c r="B3" t="n">
-        <v>57737</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -861,10 +869,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +909,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,32 +918,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,50 +942,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788683</v>
       </c>
       <c r="B4" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472158</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,13 +1038,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788686</v>
+        <v>129788704</v>
       </c>
       <c r="B9" t="n">
         <v>57737</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472112</v>
+        <v>472090</v>
       </c>
       <c r="R9" t="n">
-        <v>7028955</v>
+        <v>7028888</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1765,7 +1765,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788704</v>
+        <v>129788703</v>
       </c>
       <c r="B10" t="n">
         <v>57737</v>
@@ -1798,7 +1798,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472090</v>
+        <v>472087</v>
       </c>
       <c r="R10" t="n">
-        <v>7028888</v>
+        <v>7028909</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1904,7 +1904,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788703</v>
+        <v>129788686</v>
       </c>
       <c r="B11" t="n">
         <v>57737</v>
@@ -1937,7 +1937,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472087</v>
+        <v>472112</v>
       </c>
       <c r="R11" t="n">
-        <v>7028909</v>
+        <v>7028955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2043,65 +2043,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788716</v>
+        <v>129788707</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472440</v>
+        <v>472260</v>
       </c>
       <c r="R12" t="n">
-        <v>7028732</v>
+        <v>7028803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2136,25 +2116,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2171,7 +2140,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788721</v>
+        <v>129788716</v>
       </c>
       <c r="B13" t="n">
         <v>98794</v>
@@ -2201,7 +2170,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2226,10 +2195,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472388</v>
+        <v>472440</v>
       </c>
       <c r="R13" t="n">
-        <v>7028829</v>
+        <v>7028732</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2266,7 +2235,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2281,7 +2250,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2299,45 +2268,65 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788707</v>
+        <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472260</v>
+        <v>472388</v>
       </c>
       <c r="R14" t="n">
-        <v>7028803</v>
+        <v>7028829</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2372,14 +2361,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Gransumpskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2707,7 +2707,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R17" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2846,7 +2846,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R18" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3075,65 +3075,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788720</v>
+        <v>129788706</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>97665</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472282</v>
+        <v>472382</v>
       </c>
       <c r="R20" t="n">
-        <v>7028952</v>
+        <v>7028711</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3170,7 +3150,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3179,14 +3159,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3203,7 +3177,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788714</v>
+        <v>129788720</v>
       </c>
       <c r="B21" t="n">
         <v>98794</v>
@@ -3233,7 +3207,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3258,10 +3232,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472482</v>
+        <v>472282</v>
       </c>
       <c r="R21" t="n">
-        <v>7028718</v>
+        <v>7028952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3298,7 +3272,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,7 +3287,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B22" t="n">
-        <v>97665</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -4657,10 +4657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788672</v>
+        <v>129788682</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4668,41 +4668,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472381</v>
+        <v>472181</v>
       </c>
       <c r="R32" t="n">
-        <v>7028719</v>
+        <v>7028935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4739,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4748,7 +4753,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4769,12 +4773,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4792,42 +4796,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788699</v>
+        <v>129788722</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4839,10 +4851,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472089</v>
+        <v>472240</v>
       </c>
       <c r="R33" t="n">
-        <v>7028934</v>
+        <v>7028927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4879,7 +4891,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4888,32 +4900,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4931,7 +4924,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B34" t="n">
         <v>57737</v>
@@ -4978,10 +4971,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R34" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5018,7 +5011,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5070,65 +5063,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788672</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472381</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028719</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5145,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5180,7 +5160,27 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5198,52 +5198,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788673</v>
+        <v>129788715</v>
       </c>
       <c r="B36" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472242</v>
+        <v>472454</v>
       </c>
       <c r="R36" t="n">
-        <v>7028816</v>
+        <v>7028715</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5280,7 +5293,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5296,26 +5309,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5881,65 +5874,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788715</v>
+        <v>129788673</v>
       </c>
       <c r="B41" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472454</v>
+        <v>472242</v>
       </c>
       <c r="R41" t="n">
-        <v>7028715</v>
+        <v>7028816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,7 +5956,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5992,6 +5972,26 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,42 +6009,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788684</v>
+        <v>129788718</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>98794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6056,10 +6064,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472106</v>
+        <v>472399</v>
       </c>
       <c r="R42" t="n">
-        <v>7028852</v>
+        <v>7028764</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6096,7 +6104,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6105,32 +6113,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,50 +6137,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788684</v>
       </c>
       <c r="B43" t="n">
-        <v>98794</v>
+        <v>57737</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6203,10 +6184,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472106</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028852</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6224,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6252,13 +6233,32 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B44" t="n">
         <v>98794</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R44" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -1626,7 +1626,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788704</v>
+        <v>129788686</v>
       </c>
       <c r="B9" t="n">
         <v>57737</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472090</v>
+        <v>472112</v>
       </c>
       <c r="R9" t="n">
-        <v>7028888</v>
+        <v>7028955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1765,57 +1765,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788703</v>
+        <v>129788707</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>97665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472087</v>
+        <v>472260</v>
       </c>
       <c r="R10" t="n">
-        <v>7028909</v>
+        <v>7028803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1850,11 +1838,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1863,31 +1846,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1904,7 +1862,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788686</v>
+        <v>129788704</v>
       </c>
       <c r="B11" t="n">
         <v>57737</v>
@@ -1951,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472112</v>
+        <v>472090</v>
       </c>
       <c r="R11" t="n">
-        <v>7028955</v>
+        <v>7028888</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1991,7 +1949,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2005,7 +1963,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2043,45 +2001,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788707</v>
+        <v>129788703</v>
       </c>
       <c r="B12" t="n">
-        <v>97665</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472260</v>
+        <v>472087</v>
       </c>
       <c r="R12" t="n">
-        <v>7028803</v>
+        <v>7028909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,6 +2086,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2124,6 +2099,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2674,7 +2674,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B17" t="n">
         <v>57737</v>
@@ -2707,7 +2707,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2721,10 +2721,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R17" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2813,7 +2813,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B18" t="n">
         <v>57737</v>
@@ -2846,7 +2846,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R18" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788693</v>
+        <v>129788683</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472086</v>
+        <v>472158</v>
       </c>
       <c r="R2" t="n">
-        <v>7028965</v>
+        <v>7028919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +776,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -814,50 +814,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788719</v>
+        <v>129788693</v>
       </c>
       <c r="B3" t="n">
-        <v>98794</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -869,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472312</v>
+        <v>472086</v>
       </c>
       <c r="R3" t="n">
-        <v>7028922</v>
+        <v>7028965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,13 +910,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -942,42 +953,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788683</v>
+        <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472158</v>
+        <v>472312</v>
       </c>
       <c r="R4" t="n">
-        <v>7028919</v>
+        <v>7028922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1048,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,32 +1057,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1084,7 +1084,7 @@
         <v>129788697</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1348,57 +1348,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788698</v>
+        <v>129788707</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472086</v>
+        <v>472260</v>
       </c>
       <c r="R7" t="n">
-        <v>7028944</v>
+        <v>7028803</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,11 +1421,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1446,31 +1429,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1487,10 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788692</v>
+        <v>129788698</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1478,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1534,10 +1492,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472092</v>
+        <v>472086</v>
       </c>
       <c r="R8" t="n">
-        <v>7028968</v>
+        <v>7028944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1574,7 +1532,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788686</v>
+        <v>129788692</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1673,10 +1631,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472112</v>
+        <v>472092</v>
       </c>
       <c r="R9" t="n">
-        <v>7028955</v>
+        <v>7028968</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,7 +1671,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1765,45 +1723,57 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788707</v>
+        <v>129788686</v>
       </c>
       <c r="B10" t="n">
-        <v>97665</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472260</v>
+        <v>472112</v>
       </c>
       <c r="R10" t="n">
-        <v>7028803</v>
+        <v>7028955</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1838,6 +1808,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1846,6 +1821,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1865,7 +1865,7 @@
         <v>129788704</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>129788703</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>129788716</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>129788702</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>129788687</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>129788688</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>129788705</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         <v>129788709</v>
       </c>
       <c r="B19" t="n">
-        <v>58108</v>
+        <v>58111</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3075,45 +3075,65 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B20" t="n">
-        <v>97665</v>
+        <v>98797</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R20" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3150,7 +3170,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3159,8 +3179,14 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3180,7 +3206,7 @@
         <v>129788720</v>
       </c>
       <c r="B21" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3305,65 +3331,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788714</v>
+        <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>97668</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472482</v>
+        <v>472382</v>
       </c>
       <c r="R22" t="n">
-        <v>7028718</v>
+        <v>7028711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,14 +3415,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3436,7 +3436,7 @@
         <v>129788691</v>
       </c>
       <c r="B23" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         <v>129788685</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>129788681</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>129788696</v>
       </c>
       <c r="B26" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>79084</v>
+        <v>91625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>91622</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4254,7 +4254,7 @@
         <v>129788694</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>129788701</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4532,7 +4532,7 @@
         <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R32" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4796,50 +4796,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4851,10 +4843,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R33" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4891,7 +4883,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4900,13 +4892,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4924,42 +4935,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788699</v>
+        <v>129788722</v>
       </c>
       <c r="B34" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4971,10 +4990,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472089</v>
+        <v>472240</v>
       </c>
       <c r="R34" t="n">
-        <v>7028934</v>
+        <v>7028927</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5011,7 +5030,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5020,32 +5039,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
         <v>129788672</v>
       </c>
       <c r="B35" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5198,65 +5198,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788715</v>
+        <v>129788673</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472454</v>
+        <v>472242</v>
       </c>
       <c r="R36" t="n">
-        <v>7028715</v>
+        <v>7028816</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5293,7 +5280,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5309,6 +5296,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5326,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788689</v>
+        <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5337,46 +5344,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472086</v>
+        <v>472319</v>
       </c>
       <c r="R37" t="n">
-        <v>7028991</v>
+        <v>7028798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5413,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5422,12 +5420,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5442,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5465,10 +5464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788690</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5498,7 +5497,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5512,10 +5511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472088</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028985</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5552,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5604,10 +5603,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788700</v>
+        <v>129788690</v>
       </c>
       <c r="B39" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5637,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5651,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472091</v>
+        <v>472088</v>
       </c>
       <c r="R39" t="n">
-        <v>7028924</v>
+        <v>7028985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5691,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5743,10 +5742,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788727</v>
+        <v>129788700</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5754,37 +5753,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472319</v>
+        <v>472091</v>
       </c>
       <c r="R40" t="n">
-        <v>7028798</v>
+        <v>7028924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5821,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5830,13 +5838,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5851,12 +5858,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5874,52 +5881,65 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788673</v>
+        <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472242</v>
+        <v>472454</v>
       </c>
       <c r="R41" t="n">
-        <v>7028816</v>
+        <v>7028715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5956,7 +5976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5972,26 +5992,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6009,50 +6009,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788718</v>
+        <v>129788684</v>
       </c>
       <c r="B42" t="n">
-        <v>98794</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6064,10 +6056,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472399</v>
+        <v>472106</v>
       </c>
       <c r="R42" t="n">
-        <v>7028764</v>
+        <v>7028852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6104,7 +6096,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6113,13 +6105,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6137,42 +6148,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788684</v>
+        <v>129788718</v>
       </c>
       <c r="B43" t="n">
-        <v>57737</v>
+        <v>98797</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6184,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472106</v>
+        <v>472399</v>
       </c>
       <c r="R43" t="n">
-        <v>7028852</v>
+        <v>7028764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6224,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6233,32 +6252,13 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
         <v>129788713</v>
       </c>
       <c r="B44" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>129788695</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,42 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788719</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -722,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472312</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,32 +779,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788683</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -861,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472158</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +904,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -953,50 +942,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788693</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472086</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,13 +1038,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B27" t="n">
-        <v>91625</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R27" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>91625</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R28" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788699</v>
+        <v>129788672</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>91605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4668,46 +4668,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472089</v>
+        <v>472381</v>
       </c>
       <c r="R32" t="n">
-        <v>7028934</v>
+        <v>7028719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4739,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4753,6 +4748,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4773,12 +4769,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4796,7 +4792,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B33" t="n">
         <v>57740</v>
@@ -4843,10 +4839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R33" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4883,7 +4879,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4935,50 +4931,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B34" t="n">
-        <v>98797</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4990,10 +4978,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R34" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5030,7 +5018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5039,13 +5027,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5063,52 +5070,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788672</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472381</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028719</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5145,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5160,27 +5180,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788727</v>
+        <v>129788689</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,37 +5344,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472319</v>
+        <v>472086</v>
       </c>
       <c r="R37" t="n">
-        <v>7028798</v>
+        <v>7028991</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5420,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5420,13 +5429,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5441,12 +5449,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5464,7 +5472,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788690</v>
       </c>
       <c r="B38" t="n">
         <v>57740</v>
@@ -5497,7 +5505,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5511,10 +5519,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472088</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028985</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5559,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5603,7 +5611,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788700</v>
       </c>
       <c r="B39" t="n">
         <v>57740</v>
@@ -5636,7 +5644,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5650,10 +5658,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472091</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028924</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5698,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,10 +5750,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788727</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5753,46 +5761,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472319</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5828,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5838,12 +5837,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B43" t="n">
         <v>98797</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R43" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B44" t="n">
         <v>98797</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R44" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,50 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788719</v>
+        <v>129788683</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -730,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472312</v>
+        <v>472158</v>
       </c>
       <c r="R2" t="n">
-        <v>7028922</v>
+        <v>7028919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,13 +771,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788683</v>
+        <v>129788693</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -850,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472158</v>
+        <v>472086</v>
       </c>
       <c r="R3" t="n">
-        <v>7028919</v>
+        <v>7028965</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +901,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +915,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -942,42 +953,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788693</v>
+        <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>98797</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -989,10 +1008,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R4" t="n">
-        <v>7028965</v>
+        <v>7028922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1029,7 +1048,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,32 +1057,13 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1348,45 +1348,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788707</v>
+        <v>129788698</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472260</v>
+        <v>472086</v>
       </c>
       <c r="R7" t="n">
-        <v>7028803</v>
+        <v>7028944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1421,6 +1433,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1429,6 +1446,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1445,7 +1487,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788698</v>
+        <v>129788692</v>
       </c>
       <c r="B8" t="n">
         <v>57740</v>
@@ -1478,7 +1520,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1492,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472086</v>
+        <v>472092</v>
       </c>
       <c r="R8" t="n">
-        <v>7028944</v>
+        <v>7028968</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,7 +1574,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,7 +1626,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788692</v>
+        <v>129788686</v>
       </c>
       <c r="B9" t="n">
         <v>57740</v>
@@ -1631,10 +1673,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472092</v>
+        <v>472112</v>
       </c>
       <c r="R9" t="n">
-        <v>7028968</v>
+        <v>7028955</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1671,7 +1713,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,7 +1765,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788686</v>
+        <v>129788704</v>
       </c>
       <c r="B10" t="n">
         <v>57740</v>
@@ -1770,10 +1812,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472112</v>
+        <v>472090</v>
       </c>
       <c r="R10" t="n">
-        <v>7028955</v>
+        <v>7028888</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1810,7 +1852,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1824,7 +1866,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1862,7 +1904,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788704</v>
+        <v>129788703</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1895,7 +1937,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1909,10 +1951,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472090</v>
+        <v>472087</v>
       </c>
       <c r="R11" t="n">
-        <v>7028888</v>
+        <v>7028909</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1949,7 +1991,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2001,57 +2043,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788703</v>
+        <v>129788707</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>97668</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472087</v>
+        <v>472260</v>
       </c>
       <c r="R12" t="n">
-        <v>7028909</v>
+        <v>7028803</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2086,11 +2116,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2099,31 +2124,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2674,42 +2674,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788688</v>
+        <v>129788714</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2721,10 +2729,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472089</v>
+        <v>472482</v>
       </c>
       <c r="R17" t="n">
-        <v>7029005</v>
+        <v>7028718</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2761,7 +2769,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2770,32 +2778,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2813,7 +2802,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B18" t="n">
         <v>57740</v>
@@ -2846,7 +2835,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2860,10 +2849,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R18" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2900,7 +2889,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2914,7 +2903,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2952,27 +2941,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788709</v>
+        <v>129788705</v>
       </c>
       <c r="B19" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2980,16 +2969,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3003,10 +2988,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472246</v>
+        <v>472092</v>
       </c>
       <c r="R19" t="n">
-        <v>7028867</v>
+        <v>7028874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3043,7 +3028,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3057,7 +3042,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3075,50 +3080,46 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788714</v>
+        <v>129788709</v>
       </c>
       <c r="B20" t="n">
-        <v>98797</v>
+        <v>58111</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3130,10 +3131,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472482</v>
+        <v>472246</v>
       </c>
       <c r="R20" t="n">
-        <v>7028718</v>
+        <v>7028867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3170,7 +3171,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3179,13 +3180,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3203,65 +3203,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788720</v>
+        <v>129788706</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>97668</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472282</v>
+        <v>472382</v>
       </c>
       <c r="R21" t="n">
-        <v>7028952</v>
+        <v>7028711</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3298,7 +3278,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3307,14 +3287,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788720</v>
       </c>
       <c r="B22" t="n">
-        <v>97668</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472282</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028952</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>91625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>91625</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788689</v>
+        <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,46 +5344,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472086</v>
+        <v>472319</v>
       </c>
       <c r="R37" t="n">
-        <v>7028991</v>
+        <v>7028798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5420,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5429,12 +5420,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -5449,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5472,7 +5464,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788690</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
         <v>57740</v>
@@ -5505,7 +5497,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5519,10 +5511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472088</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028985</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5559,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5611,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788700</v>
+        <v>129788690</v>
       </c>
       <c r="B39" t="n">
         <v>57740</v>
@@ -5644,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5658,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472091</v>
+        <v>472088</v>
       </c>
       <c r="R39" t="n">
-        <v>7028924</v>
+        <v>7028985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5698,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5750,10 +5742,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788727</v>
+        <v>129788700</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5761,37 +5753,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472319</v>
+        <v>472091</v>
       </c>
       <c r="R40" t="n">
-        <v>7028798</v>
+        <v>7028924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5828,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5837,13 +5838,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B43" t="n">
         <v>98797</v>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,7 +6276,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B44" t="n">
         <v>98797</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R44" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -956,7 +956,7 @@
         <v>129788719</v>
       </c>
       <c r="B4" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>129788724</v>
       </c>
       <c r="B6" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>129788707</v>
       </c>
       <c r="B12" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>129788716</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>129788721</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129788702</v>
+        <v>129788687</v>
       </c>
       <c r="B15" t="n">
         <v>57740</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472087</v>
+        <v>472094</v>
       </c>
       <c r="R15" t="n">
-        <v>7028916</v>
+        <v>7029010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2535,7 +2535,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129788687</v>
+        <v>129788702</v>
       </c>
       <c r="B16" t="n">
         <v>57740</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472094</v>
+        <v>472087</v>
       </c>
       <c r="R16" t="n">
-        <v>7029010</v>
+        <v>7028916</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2674,50 +2674,46 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788714</v>
+        <v>129788709</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>58111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2729,10 +2725,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472482</v>
+        <v>472246</v>
       </c>
       <c r="R17" t="n">
-        <v>7028718</v>
+        <v>7028867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2769,7 +2765,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2778,13 +2774,12 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2802,42 +2797,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788688</v>
+        <v>129788720</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2849,10 +2852,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472089</v>
+        <v>472282</v>
       </c>
       <c r="R18" t="n">
-        <v>7029005</v>
+        <v>7028952</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2889,7 +2892,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2898,32 +2901,13 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2941,42 +2925,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788705</v>
+        <v>129788714</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2988,10 +2980,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472092</v>
+        <v>472482</v>
       </c>
       <c r="R19" t="n">
-        <v>7028874</v>
+        <v>7028718</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3028,7 +3020,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3037,32 +3029,13 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,27 +3053,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788709</v>
+        <v>129788688</v>
       </c>
       <c r="B20" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3108,16 +3081,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3131,10 +3100,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472246</v>
+        <v>472089</v>
       </c>
       <c r="R20" t="n">
-        <v>7028867</v>
+        <v>7029005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3171,7 +3140,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3186,6 +3155,26 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3203,45 +3192,57 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788706</v>
+        <v>129788705</v>
       </c>
       <c r="B21" t="n">
-        <v>97668</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472382</v>
+        <v>472092</v>
       </c>
       <c r="R21" t="n">
-        <v>7028711</v>
+        <v>7028874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3278,7 +3279,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3289,6 +3290,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3305,65 +3331,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788720</v>
+        <v>129788706</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>97669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472282</v>
+        <v>472382</v>
       </c>
       <c r="R22" t="n">
-        <v>7028952</v>
+        <v>7028711</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3406,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,14 +3415,8 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B27" t="n">
-        <v>91625</v>
+        <v>79088</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R27" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R28" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4251,42 +4251,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788694</v>
+        <v>129788723</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4298,10 +4306,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472085</v>
+        <v>472131</v>
       </c>
       <c r="R29" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4347,32 +4355,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4390,7 +4379,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788701</v>
+        <v>129788694</v>
       </c>
       <c r="B30" t="n">
         <v>57740</v>
@@ -4423,7 +4412,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4437,10 +4426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472090</v>
+        <v>472085</v>
       </c>
       <c r="R30" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4477,7 +4466,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4529,50 +4518,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788723</v>
+        <v>129788701</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>57740</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4584,7 +4565,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472131</v>
+        <v>472090</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4624,7 +4605,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4633,13 +4614,32 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788672</v>
+        <v>129788699</v>
       </c>
       <c r="B32" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4668,41 +4668,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472381</v>
+        <v>472089</v>
       </c>
       <c r="R32" t="n">
-        <v>7028719</v>
+        <v>7028934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4739,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4748,7 +4753,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4769,12 +4773,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4792,7 +4796,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788699</v>
+        <v>129788682</v>
       </c>
       <c r="B33" t="n">
         <v>57740</v>
@@ -4839,10 +4843,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472089</v>
+        <v>472181</v>
       </c>
       <c r="R33" t="n">
-        <v>7028934</v>
+        <v>7028935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4879,7 +4883,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4931,10 +4935,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788682</v>
+        <v>129788672</v>
       </c>
       <c r="B34" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4942,46 +4946,41 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472181</v>
+        <v>472381</v>
       </c>
       <c r="R34" t="n">
-        <v>7028935</v>
+        <v>7028719</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5018,7 +5017,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5027,6 +5026,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
         <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>129788673</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788700</v>
       </c>
       <c r="B38" t="n">
         <v>57740</v>
@@ -5511,10 +5511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472091</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028924</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5603,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788689</v>
       </c>
       <c r="B39" t="n">
         <v>57740</v>
@@ -5636,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5650,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472086</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028991</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5742,7 +5742,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788690</v>
       </c>
       <c r="B40" t="n">
         <v>57740</v>
@@ -5775,7 +5775,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472088</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028985</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5884,7 +5884,7 @@
         <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788718</v>
+        <v>129788713</v>
       </c>
       <c r="B43" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472399</v>
+        <v>472513</v>
       </c>
       <c r="R43" t="n">
-        <v>7028764</v>
+        <v>7028648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6276,10 +6276,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788713</v>
+        <v>129788718</v>
       </c>
       <c r="B44" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472513</v>
+        <v>472399</v>
       </c>
       <c r="R44" t="n">
-        <v>7028648</v>
+        <v>7028764</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -2043,45 +2043,65 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788707</v>
+        <v>129788716</v>
       </c>
       <c r="B12" t="n">
-        <v>97669</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472260</v>
+        <v>472440</v>
       </c>
       <c r="R12" t="n">
-        <v>7028803</v>
+        <v>7028732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2116,14 +2136,25 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2140,7 +2171,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788716</v>
+        <v>129788721</v>
       </c>
       <c r="B13" t="n">
         <v>98798</v>
@@ -2170,7 +2201,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2195,10 +2226,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472440</v>
+        <v>472388</v>
       </c>
       <c r="R13" t="n">
-        <v>7028732</v>
+        <v>7028829</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2235,7 +2266,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,7 +2281,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2268,65 +2299,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788721</v>
+        <v>129788707</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>97669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472388</v>
+        <v>472260</v>
       </c>
       <c r="R14" t="n">
-        <v>7028829</v>
+        <v>7028803</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,25 +2372,14 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Gransumpskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2674,46 +2674,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788709</v>
+        <v>129788720</v>
       </c>
       <c r="B17" t="n">
-        <v>58111</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2725,10 +2729,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472246</v>
+        <v>472282</v>
       </c>
       <c r="R17" t="n">
-        <v>7028867</v>
+        <v>7028952</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2765,7 +2769,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2774,6 +2778,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2797,7 +2802,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788720</v>
+        <v>129788714</v>
       </c>
       <c r="B18" t="n">
         <v>98798</v>
@@ -2827,7 +2832,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472282</v>
+        <v>472482</v>
       </c>
       <c r="R18" t="n">
-        <v>7028952</v>
+        <v>7028718</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2907,7 +2912,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2925,50 +2930,42 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788714</v>
+        <v>129788688</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2980,10 +2977,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472482</v>
+        <v>472089</v>
       </c>
       <c r="R19" t="n">
-        <v>7028718</v>
+        <v>7029005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3020,7 +3017,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3029,13 +3026,32 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3053,7 +3069,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B20" t="n">
         <v>57740</v>
@@ -3086,7 +3102,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3100,10 +3116,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R20" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3140,7 +3156,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3154,7 +3170,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3192,27 +3208,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788705</v>
+        <v>129788709</v>
       </c>
       <c r="B21" t="n">
-        <v>57740</v>
+        <v>58111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3220,12 +3236,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3239,10 +3259,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472092</v>
+        <v>472246</v>
       </c>
       <c r="R21" t="n">
-        <v>7028874</v>
+        <v>7028867</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3279,7 +3299,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3293,27 +3313,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3989,10 +3989,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>79088</v>
+        <v>91626</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,26 +4000,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472407</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>I en klen granstubbe i granskog på fuktig mark.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,26 +4131,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472415</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028768</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788699</v>
+        <v>129788682</v>
       </c>
       <c r="B32" t="n">
         <v>57740</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472089</v>
+        <v>472181</v>
       </c>
       <c r="R32" t="n">
-        <v>7028934</v>
+        <v>7028935</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4796,42 +4796,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788682</v>
+        <v>129788722</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4843,10 +4851,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472181</v>
+        <v>472240</v>
       </c>
       <c r="R33" t="n">
-        <v>7028935</v>
+        <v>7028927</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4883,7 +4891,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4892,32 +4900,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5070,50 +5059,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788699</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5125,10 +5106,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472089</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028934</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5146,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5174,13 +5155,32 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -4657,7 +4657,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B32" t="n">
         <v>57740</v>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R32" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4796,50 +4796,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788722</v>
+        <v>129788682</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4851,10 +4843,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472240</v>
+        <v>472181</v>
       </c>
       <c r="R33" t="n">
-        <v>7028927</v>
+        <v>7028935</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4891,7 +4883,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4900,13 +4892,32 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -5059,42 +5070,50 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788699</v>
+        <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5106,10 +5125,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472089</v>
+        <v>472240</v>
       </c>
       <c r="R35" t="n">
-        <v>7028934</v>
+        <v>7028927</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5146,7 +5165,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5155,32 +5174,13 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788673</v>
+        <v>129788727</v>
       </c>
       <c r="B36" t="n">
-        <v>91606</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5209,30 +5209,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5240,10 +5236,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472242</v>
+        <v>472319</v>
       </c>
       <c r="R36" t="n">
-        <v>7028816</v>
+        <v>7028798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5280,7 +5276,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5310,12 +5306,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5333,10 +5329,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788727</v>
+        <v>129788673</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>91606</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5344,26 +5340,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472319</v>
+        <v>472242</v>
       </c>
       <c r="R37" t="n">
-        <v>7028798</v>
+        <v>7028816</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -675,42 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788719</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -722,10 +730,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472312</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,32 +779,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,7 +803,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788683</v>
       </c>
       <c r="B3" t="n">
         <v>57740</v>
@@ -861,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472158</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +904,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -953,50 +942,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788693</v>
       </c>
       <c r="B4" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1008,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472086</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028965</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1029,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1057,13 +1038,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,42 +1081,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788697</v>
+        <v>129788724</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1128,10 +1136,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472086</v>
+        <v>472142</v>
       </c>
       <c r="R5" t="n">
-        <v>7028958</v>
+        <v>7028942</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,32 +1185,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,50 +1209,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788724</v>
+        <v>129788697</v>
       </c>
       <c r="B6" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1275,10 +1256,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472142</v>
+        <v>472086</v>
       </c>
       <c r="R6" t="n">
-        <v>7028942</v>
+        <v>7028958</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,7 +1296,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,13 +1305,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788698</v>
+        <v>129788703</v>
       </c>
       <c r="B7" t="n">
         <v>57740</v>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472086</v>
+        <v>472087</v>
       </c>
       <c r="R7" t="n">
-        <v>7028944</v>
+        <v>7028909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1487,42 +1487,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788692</v>
+        <v>129788716</v>
       </c>
       <c r="B8" t="n">
-        <v>57740</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472092</v>
+        <v>472440</v>
       </c>
       <c r="R8" t="n">
-        <v>7028968</v>
+        <v>7028732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1574,7 +1582,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,32 +1591,13 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1626,42 +1615,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788686</v>
+        <v>129788721</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1673,10 +1670,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472112</v>
+        <v>472388</v>
       </c>
       <c r="R9" t="n">
-        <v>7028955</v>
+        <v>7028829</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,7 +1710,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1722,32 +1719,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1765,57 +1743,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788704</v>
+        <v>129788707</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>97686</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472090</v>
+        <v>472260</v>
       </c>
       <c r="R10" t="n">
-        <v>7028888</v>
+        <v>7028803</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1850,11 +1816,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1863,31 +1824,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1904,7 +1840,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788703</v>
+        <v>129788698</v>
       </c>
       <c r="B11" t="n">
         <v>57740</v>
@@ -1951,10 +1887,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472087</v>
+        <v>472086</v>
       </c>
       <c r="R11" t="n">
-        <v>7028909</v>
+        <v>7028944</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1991,7 +1927,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2005,7 +1941,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2043,50 +1979,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788716</v>
+        <v>129788692</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2098,10 +2026,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472440</v>
+        <v>472092</v>
       </c>
       <c r="R12" t="n">
-        <v>7028732</v>
+        <v>7028968</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2138,7 +2066,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2147,13 +2075,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2171,50 +2118,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788721</v>
+        <v>129788686</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2226,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472388</v>
+        <v>472112</v>
       </c>
       <c r="R13" t="n">
-        <v>7028829</v>
+        <v>7028955</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2266,7 +2205,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2275,13 +2214,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2299,45 +2257,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788707</v>
+        <v>129788704</v>
       </c>
       <c r="B14" t="n">
-        <v>97669</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472260</v>
+        <v>472090</v>
       </c>
       <c r="R14" t="n">
-        <v>7028803</v>
+        <v>7028888</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2372,6 +2342,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2380,6 +2355,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2396,7 +2396,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129788687</v>
+        <v>129788702</v>
       </c>
       <c r="B15" t="n">
         <v>57740</v>
@@ -2443,10 +2443,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472094</v>
+        <v>472087</v>
       </c>
       <c r="R15" t="n">
-        <v>7029010</v>
+        <v>7028916</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2535,7 +2535,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129788702</v>
+        <v>129788687</v>
       </c>
       <c r="B16" t="n">
         <v>57740</v>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472087</v>
+        <v>472094</v>
       </c>
       <c r="R16" t="n">
-        <v>7028916</v>
+        <v>7029010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2677,7 +2677,7 @@
         <v>129788720</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>129788714</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2930,57 +2930,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788688</v>
+        <v>129788706</v>
       </c>
       <c r="B19" t="n">
-        <v>57740</v>
+        <v>97686</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472089</v>
+        <v>472382</v>
       </c>
       <c r="R19" t="n">
-        <v>7029005</v>
+        <v>7028711</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3017,7 +3005,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3028,31 +3016,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3069,7 +3032,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788705</v>
+        <v>129788688</v>
       </c>
       <c r="B20" t="n">
         <v>57740</v>
@@ -3102,7 +3065,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3116,10 +3079,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R20" t="n">
-        <v>7028874</v>
+        <v>7029005</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3156,7 +3119,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3170,7 +3133,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3208,27 +3171,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788709</v>
+        <v>129788705</v>
       </c>
       <c r="B21" t="n">
-        <v>58111</v>
+        <v>57740</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3236,16 +3199,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3259,10 +3218,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472246</v>
+        <v>472092</v>
       </c>
       <c r="R21" t="n">
-        <v>7028867</v>
+        <v>7028874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3299,7 +3258,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,7 +3272,27 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3331,10 +3310,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788709</v>
       </c>
       <c r="B22" t="n">
-        <v>97669</v>
+        <v>58112</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3342,34 +3321,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472246</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3401,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3417,6 +3412,11 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3992,7 +3992,7 @@
         <v>129788725</v>
       </c>
       <c r="B27" t="n">
-        <v>91626</v>
+        <v>91643</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>129788726</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4251,50 +4251,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788723</v>
+        <v>129788694</v>
       </c>
       <c r="B29" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4306,10 +4298,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472131</v>
+        <v>472085</v>
       </c>
       <c r="R29" t="n">
-        <v>7028919</v>
+        <v>7028966</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4346,7 +4338,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4355,13 +4347,32 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4379,7 +4390,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788694</v>
+        <v>129788701</v>
       </c>
       <c r="B30" t="n">
         <v>57740</v>
@@ -4412,7 +4423,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4426,10 +4437,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472085</v>
+        <v>472090</v>
       </c>
       <c r="R30" t="n">
-        <v>7028966</v>
+        <v>7028919</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4466,7 +4477,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4518,42 +4529,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788701</v>
+        <v>129788723</v>
       </c>
       <c r="B31" t="n">
-        <v>57740</v>
+        <v>98815</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4565,7 +4584,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472090</v>
+        <v>472131</v>
       </c>
       <c r="R31" t="n">
         <v>7028919</v>
@@ -4605,7 +4624,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4614,32 +4633,13 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4657,10 +4657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788699</v>
+        <v>129788672</v>
       </c>
       <c r="B32" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4668,46 +4668,41 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472089</v>
+        <v>472381</v>
       </c>
       <c r="R32" t="n">
-        <v>7028934</v>
+        <v>7028719</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4744,7 +4739,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4753,6 +4748,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4773,12 +4769,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4796,7 +4792,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788682</v>
+        <v>129788699</v>
       </c>
       <c r="B33" t="n">
         <v>57740</v>
@@ -4843,10 +4839,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472181</v>
+        <v>472089</v>
       </c>
       <c r="R33" t="n">
-        <v>7028935</v>
+        <v>7028934</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4883,7 +4879,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4935,10 +4931,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788672</v>
+        <v>129788682</v>
       </c>
       <c r="B34" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4946,41 +4942,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472381</v>
+        <v>472181</v>
       </c>
       <c r="R34" t="n">
-        <v>7028719</v>
+        <v>7028935</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5017,7 +5018,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5026,7 +5027,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -5047,12 +5047,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5073,7 +5073,7 @@
         <v>129788722</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5198,48 +5198,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788727</v>
+        <v>129788715</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>98815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472319</v>
+        <v>472454</v>
       </c>
       <c r="R36" t="n">
-        <v>7028798</v>
+        <v>7028715</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5276,7 +5293,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5292,26 +5309,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5332,7 +5329,7 @@
         <v>129788673</v>
       </c>
       <c r="B37" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5464,10 +5461,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788700</v>
+        <v>129788727</v>
       </c>
       <c r="B38" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5475,46 +5472,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472091</v>
+        <v>472319</v>
       </c>
       <c r="R38" t="n">
-        <v>7028924</v>
+        <v>7028798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5539,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,12 +5548,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5580,12 +5569,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5881,50 +5870,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788715</v>
+        <v>129788700</v>
       </c>
       <c r="B41" t="n">
-        <v>98798</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5936,10 +5917,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472454</v>
+        <v>472091</v>
       </c>
       <c r="R41" t="n">
-        <v>7028715</v>
+        <v>7028924</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,7 +5957,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5985,13 +5966,32 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6151,7 +6151,7 @@
         <v>129788713</v>
       </c>
       <c r="B43" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
         <v>129788718</v>
       </c>
       <c r="B44" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         <v>129788717</v>
       </c>
       <c r="B46" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -1348,7 +1348,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788698</v>
+        <v>129788704</v>
       </c>
       <c r="B7" t="n">
         <v>57741</v>
@@ -1381,7 +1381,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472086</v>
+        <v>472090</v>
       </c>
       <c r="R7" t="n">
-        <v>7028944</v>
+        <v>7028888</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1487,7 +1487,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788692</v>
+        <v>129788703</v>
       </c>
       <c r="B8" t="n">
         <v>57741</v>
@@ -1520,7 +1520,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472092</v>
+        <v>472087</v>
       </c>
       <c r="R8" t="n">
-        <v>7028968</v>
+        <v>7028909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1626,42 +1626,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788686</v>
+        <v>129788716</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>98831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1673,10 +1681,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472112</v>
+        <v>472440</v>
       </c>
       <c r="R9" t="n">
-        <v>7028955</v>
+        <v>7028732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1713,7 +1721,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1722,32 +1730,13 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1765,42 +1754,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788704</v>
+        <v>129788721</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>98831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1812,10 +1809,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472090</v>
+        <v>472388</v>
       </c>
       <c r="R10" t="n">
-        <v>7028888</v>
+        <v>7028829</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1852,7 +1849,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1861,32 +1858,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1904,57 +1882,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788703</v>
+        <v>129788707</v>
       </c>
       <c r="B11" t="n">
-        <v>57741</v>
+        <v>97702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472087</v>
+        <v>472260</v>
       </c>
       <c r="R11" t="n">
-        <v>7028909</v>
+        <v>7028803</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1989,11 +1955,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -2002,31 +1963,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2043,50 +1979,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788716</v>
+        <v>129788698</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2098,10 +2026,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472440</v>
+        <v>472086</v>
       </c>
       <c r="R12" t="n">
-        <v>7028732</v>
+        <v>7028944</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2138,7 +2066,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2147,13 +2075,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2171,50 +2118,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788721</v>
+        <v>129788692</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>57741</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2226,10 +2165,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472388</v>
+        <v>472092</v>
       </c>
       <c r="R13" t="n">
-        <v>7028829</v>
+        <v>7028968</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2266,7 +2205,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2275,13 +2214,32 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2299,45 +2257,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788707</v>
+        <v>129788686</v>
       </c>
       <c r="B14" t="n">
-        <v>97702</v>
+        <v>57741</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472260</v>
+        <v>472112</v>
       </c>
       <c r="R14" t="n">
-        <v>7028803</v>
+        <v>7028955</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2372,6 +2342,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2380,6 +2355,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2674,65 +2674,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788720</v>
+        <v>129788706</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>97702</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472282</v>
+        <v>472382</v>
       </c>
       <c r="R17" t="n">
-        <v>7028952</v>
+        <v>7028711</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2769,7 +2749,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2778,14 +2758,8 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2802,50 +2776,46 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788714</v>
+        <v>129788709</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>58113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2857,10 +2827,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472482</v>
+        <v>472246</v>
       </c>
       <c r="R18" t="n">
-        <v>7028718</v>
+        <v>7028867</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2897,7 +2867,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2906,13 +2876,12 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2930,27 +2899,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788709</v>
+        <v>129788688</v>
       </c>
       <c r="B19" t="n">
-        <v>58113</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2958,16 +2927,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2981,10 +2946,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472246</v>
+        <v>472089</v>
       </c>
       <c r="R19" t="n">
-        <v>7028867</v>
+        <v>7029005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3021,7 +2986,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3036,6 +3001,26 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3053,7 +3038,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788688</v>
+        <v>129788705</v>
       </c>
       <c r="B20" t="n">
         <v>57741</v>
@@ -3086,7 +3071,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3100,10 +3085,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472089</v>
+        <v>472092</v>
       </c>
       <c r="R20" t="n">
-        <v>7029005</v>
+        <v>7028874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3140,7 +3125,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3154,7 +3139,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3192,42 +3177,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788705</v>
+        <v>129788720</v>
       </c>
       <c r="B21" t="n">
-        <v>57741</v>
+        <v>98831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3239,10 +3232,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472092</v>
+        <v>472282</v>
       </c>
       <c r="R21" t="n">
-        <v>7028874</v>
+        <v>7028952</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3279,7 +3272,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3288,32 +3281,13 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3331,45 +3305,65 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788706</v>
+        <v>129788714</v>
       </c>
       <c r="B22" t="n">
-        <v>97702</v>
+        <v>98831</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472382</v>
+        <v>472482</v>
       </c>
       <c r="R22" t="n">
-        <v>7028711</v>
+        <v>7028718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3406,7 +3400,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3415,8 +3409,14 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -5333,65 +5333,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788715</v>
+        <v>129788727</v>
       </c>
       <c r="B37" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472454</v>
+        <v>472319</v>
       </c>
       <c r="R37" t="n">
-        <v>7028715</v>
+        <v>7028798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5428,7 +5411,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5444,6 +5427,26 @@
       <c r="AH37" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5461,10 +5464,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788727</v>
+        <v>129788689</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5472,37 +5475,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472319</v>
+        <v>472086</v>
       </c>
       <c r="R38" t="n">
-        <v>7028798</v>
+        <v>7028991</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5539,7 +5551,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5548,13 +5560,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -5569,12 +5580,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5592,7 +5603,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788689</v>
+        <v>129788690</v>
       </c>
       <c r="B39" t="n">
         <v>57741</v>
@@ -5625,7 +5636,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5639,10 +5650,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472086</v>
+        <v>472088</v>
       </c>
       <c r="R39" t="n">
-        <v>7028991</v>
+        <v>7028985</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5679,7 +5690,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5731,7 +5742,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788690</v>
+        <v>129788700</v>
       </c>
       <c r="B40" t="n">
         <v>57741</v>
@@ -5764,7 +5775,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5778,10 +5789,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472088</v>
+        <v>472091</v>
       </c>
       <c r="R40" t="n">
-        <v>7028985</v>
+        <v>7028924</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5818,7 +5829,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5870,42 +5881,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788700</v>
+        <v>129788715</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>98831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5917,10 +5936,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472091</v>
+        <v>472454</v>
       </c>
       <c r="R41" t="n">
-        <v>7028924</v>
+        <v>7028715</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5957,7 +5976,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5966,32 +5985,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129788683</v>
+        <v>129788672</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,46 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472158</v>
+        <v>472381</v>
       </c>
       <c r="R2" t="n">
-        <v>7028919</v>
+        <v>7028719</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
+          <t>Växer i en upplyft granlåga i granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,12 +766,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -791,12 +787,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -814,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129788693</v>
+        <v>129788673</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,46 +821,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472086</v>
+        <v>472242</v>
       </c>
       <c r="R3" t="n">
-        <v>7028965</v>
+        <v>7028816</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +901,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -930,12 +922,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -953,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129788719</v>
+        <v>129788726</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,54 +956,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472312</v>
+        <v>472415</v>
       </c>
       <c r="R4" t="n">
-        <v>7028922</v>
+        <v>7028768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1048,7 +1023,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
+          <t>På flera granar i granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,6 +1039,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1081,57 +1076,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129788697</v>
+        <v>129788727</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472086</v>
+        <v>472319</v>
       </c>
       <c r="R5" t="n">
-        <v>7028958</v>
+        <v>7028798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,7 +1154,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Enstaka på gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,12 +1163,13 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1197,12 +1184,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1220,50 +1207,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129788724</v>
+        <v>129788681</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1275,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>472142</v>
+        <v>472502</v>
       </c>
       <c r="R6" t="n">
-        <v>7028942</v>
+        <v>7028703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,7 +1294,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
+          <t>Ringhack, äldre, ett par meter upp på en granstam.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,13 +1303,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1348,10 +1346,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129788704</v>
+        <v>129788682</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1395,10 +1393,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>472090</v>
+        <v>472181</v>
       </c>
       <c r="R7" t="n">
-        <v>7028888</v>
+        <v>7028935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1435,7 +1433,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1447,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1487,10 +1485,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129788703</v>
+        <v>129788683</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1520,7 +1518,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1534,10 +1532,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>472087</v>
+        <v>472158</v>
       </c>
       <c r="R8" t="n">
-        <v>7028909</v>
+        <v>7028919</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1574,7 +1572,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i barrblandskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1626,50 +1624,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129788716</v>
+        <v>129788684</v>
       </c>
       <c r="B9" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1681,10 +1671,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>472440</v>
+        <v>472106</v>
       </c>
       <c r="R9" t="n">
-        <v>7028732</v>
+        <v>7028852</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1721,7 +1711,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1730,13 +1720,32 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1754,50 +1763,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129788721</v>
+        <v>129788685</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1809,10 +1810,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>472388</v>
+        <v>472106</v>
       </c>
       <c r="R10" t="n">
-        <v>7028829</v>
+        <v>7028952</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1849,7 +1850,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
+          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1858,13 +1859,32 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Gransumpskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1882,45 +1902,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129788707</v>
+        <v>129788686</v>
       </c>
       <c r="B11" t="n">
-        <v>97702</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>472260</v>
+        <v>472112</v>
       </c>
       <c r="R11" t="n">
-        <v>7028803</v>
+        <v>7028955</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1955,6 +1987,11 @@
           <t>2025-11-21</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1963,6 +2000,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1979,10 +2041,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129788698</v>
+        <v>129788687</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2012,7 +2074,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2026,10 +2088,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>472086</v>
+        <v>472094</v>
       </c>
       <c r="R12" t="n">
-        <v>7028944</v>
+        <v>7029010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,7 +2128,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2118,10 +2180,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129788692</v>
+        <v>129788688</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2165,10 +2227,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>472092</v>
+        <v>472089</v>
       </c>
       <c r="R13" t="n">
-        <v>7028968</v>
+        <v>7029005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2205,7 +2267,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2257,10 +2319,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129788686</v>
+        <v>129788689</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2304,10 +2366,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>472112</v>
+        <v>472086</v>
       </c>
       <c r="R14" t="n">
-        <v>7028955</v>
+        <v>7028991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,7 +2406,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2396,10 +2458,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129788702</v>
+        <v>129788690</v>
       </c>
       <c r="B15" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2429,7 +2491,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2443,10 +2505,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>472087</v>
+        <v>472088</v>
       </c>
       <c r="R15" t="n">
-        <v>7028916</v>
+        <v>7028985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2483,7 +2545,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2497,7 +2559,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2535,10 +2597,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129788687</v>
+        <v>129788691</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2582,10 +2644,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>472094</v>
+        <v>472096</v>
       </c>
       <c r="R16" t="n">
-        <v>7029010</v>
+        <v>7028977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2622,7 +2684,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2674,45 +2736,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129788706</v>
+        <v>129788692</v>
       </c>
       <c r="B17" t="n">
-        <v>97702</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>472382</v>
+        <v>472092</v>
       </c>
       <c r="R17" t="n">
-        <v>7028711</v>
+        <v>7028968</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2823,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt!</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2760,6 +2834,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2776,27 +2875,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129788709</v>
+        <v>129788693</v>
       </c>
       <c r="B18" t="n">
-        <v>58113</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2804,16 +2903,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2827,10 +2922,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>472246</v>
+        <v>472086</v>
       </c>
       <c r="R18" t="n">
-        <v>7028867</v>
+        <v>7028965</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2867,7 +2962,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2882,6 +2977,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2899,10 +3014,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129788688</v>
+        <v>129788694</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2932,7 +3047,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2946,10 +3061,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>472089</v>
+        <v>472085</v>
       </c>
       <c r="R19" t="n">
-        <v>7029005</v>
+        <v>7028966</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2986,7 +3101,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3038,10 +3153,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129788705</v>
+        <v>129788695</v>
       </c>
       <c r="B20" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3071,7 +3186,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3085,10 +3200,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>472092</v>
+        <v>472086</v>
       </c>
       <c r="R20" t="n">
-        <v>7028874</v>
+        <v>7028963</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3125,7 +3240,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3139,7 +3254,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3177,50 +3292,42 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129788720</v>
+        <v>129788696</v>
       </c>
       <c r="B21" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3232,10 +3339,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>472282</v>
+        <v>472086</v>
       </c>
       <c r="R21" t="n">
-        <v>7028952</v>
+        <v>7028953</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3272,7 +3379,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3281,13 +3388,32 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3305,50 +3431,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129788714</v>
+        <v>129788697</v>
       </c>
       <c r="B22" t="n">
-        <v>98831</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3360,10 +3478,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>472482</v>
+        <v>472086</v>
       </c>
       <c r="R22" t="n">
-        <v>7028718</v>
+        <v>7028958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,7 +3518,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3409,13 +3527,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3433,10 +3570,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129788691</v>
+        <v>129788698</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3466,7 +3603,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3480,10 +3617,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>472096</v>
+        <v>472086</v>
       </c>
       <c r="R23" t="n">
-        <v>7028977</v>
+        <v>7028944</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3520,7 +3657,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3572,10 +3709,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129788685</v>
+        <v>129788699</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3605,7 +3742,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3619,10 +3756,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>472106</v>
+        <v>472089</v>
       </c>
       <c r="R24" t="n">
-        <v>7028952</v>
+        <v>7028934</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3659,7 +3796,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, högt upp på en gran.</t>
+          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3711,10 +3848,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129788681</v>
+        <v>129788700</v>
       </c>
       <c r="B25" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3758,10 +3895,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>472502</v>
+        <v>472091</v>
       </c>
       <c r="R25" t="n">
-        <v>7028703</v>
+        <v>7028924</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3798,7 +3935,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, ett par meter upp på en granstam.</t>
+          <t>Ringhack (savhack), äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3812,7 +3949,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -3850,10 +3987,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129788696</v>
+        <v>129788701</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3897,10 +4034,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>472086</v>
+        <v>472090</v>
       </c>
       <c r="R26" t="n">
-        <v>7028953</v>
+        <v>7028919</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3937,7 +4074,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3989,10 +4126,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129788726</v>
+        <v>129788702</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4000,37 +4137,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>472415</v>
+        <v>472087</v>
       </c>
       <c r="R27" t="n">
-        <v>7028768</v>
+        <v>7028916</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4067,7 +4213,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar i granskog.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4076,13 +4222,12 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -4097,12 +4242,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4120,10 +4265,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129788725</v>
+        <v>129788703</v>
       </c>
       <c r="B28" t="n">
-        <v>91659</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4131,37 +4276,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>472407</v>
+        <v>472087</v>
       </c>
       <c r="R28" t="n">
-        <v>7028826</v>
+        <v>7028909</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4198,7 +4352,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>I en klen granstubbe i granskog på fuktig mark.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4207,13 +4361,12 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -4228,12 +4381,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4251,10 +4404,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129788694</v>
+        <v>129788704</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4284,7 +4437,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4298,10 +4451,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>472085</v>
+        <v>472090</v>
       </c>
       <c r="R29" t="n">
-        <v>7028966</v>
+        <v>7028888</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4338,7 +4491,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
+          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4352,7 +4505,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4390,10 +4543,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129788701</v>
+        <v>129788705</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4423,7 +4576,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4437,10 +4590,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>472090</v>
+        <v>472092</v>
       </c>
       <c r="R30" t="n">
-        <v>7028919</v>
+        <v>7028874</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4477,7 +4630,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Ringhack (savhack), färska och äldre, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4491,7 +4644,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4529,50 +4682,46 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129788723</v>
+        <v>129788709</v>
       </c>
       <c r="B31" t="n">
-        <v>98831</v>
+        <v>58327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4584,10 +4733,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>472131</v>
+        <v>472246</v>
       </c>
       <c r="R31" t="n">
-        <v>7028919</v>
+        <v>7028867</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4624,7 +4773,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
+          <t>1 individ med lockläte i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4633,7 +4782,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4657,52 +4805,65 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129788672</v>
+        <v>129788713</v>
       </c>
       <c r="B32" t="n">
-        <v>91639</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>472381</v>
+        <v>472513</v>
       </c>
       <c r="R32" t="n">
-        <v>7028719</v>
+        <v>7028648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4739,7 +4900,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Växer i en upplyft granlåga i granskog.</t>
+          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4754,27 +4915,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4792,42 +4933,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129788699</v>
+        <v>129788714</v>
       </c>
       <c r="B33" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4839,10 +4988,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>472089</v>
+        <v>472482</v>
       </c>
       <c r="R33" t="n">
-        <v>7028934</v>
+        <v>7028718</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4879,7 +5028,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 22 plantor inom ca 1 m2 yta i en liten sänka intill en stående död klen delvis barkavskalad gran med potentiella födosökspår efter tretåig hackspett i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4888,32 +5037,13 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4931,42 +5061,50 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129788682</v>
+        <v>129788715</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4978,10 +5116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>472181</v>
+        <v>472454</v>
       </c>
       <c r="R34" t="n">
-        <v>7028935</v>
+        <v>7028715</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5018,7 +5156,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran i granskog.</t>
+          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5027,32 +5165,13 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -5070,10 +5189,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129788722</v>
+        <v>129788716</v>
       </c>
       <c r="B35" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5100,7 +5219,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5125,10 +5244,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>472240</v>
+        <v>472440</v>
       </c>
       <c r="R35" t="n">
-        <v>7028927</v>
+        <v>7028732</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5165,7 +5284,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
+          <t>Minst 40 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5198,52 +5317,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129788673</v>
+        <v>129788717</v>
       </c>
       <c r="B36" t="n">
-        <v>91639</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>472242</v>
+        <v>472404</v>
       </c>
       <c r="R36" t="n">
-        <v>7028816</v>
+        <v>7028751</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5280,7 +5412,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Växer i en smal upplyft granlåga i barrblandskog.</t>
+          <t>Minst 18 plantor inom ca 1 m2 yta i äldre storvuxen granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5295,27 +5427,7 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5333,48 +5445,65 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129788727</v>
+        <v>129788718</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>472319</v>
+        <v>472399</v>
       </c>
       <c r="R37" t="n">
-        <v>7028798</v>
+        <v>7028764</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5411,7 +5540,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Enstaka på gran.</t>
+          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5426,27 +5555,7 @@
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5464,42 +5573,50 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129788689</v>
+        <v>129788719</v>
       </c>
       <c r="B38" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5511,10 +5628,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>472086</v>
+        <v>472312</v>
       </c>
       <c r="R38" t="n">
-        <v>7028991</v>
+        <v>7028922</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5551,7 +5668,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran vid hyggeskanten.</t>
+          <t>Minst 13 plantor och 4 vinterståndare inom ca 3 m2 yta i granskog. Snötäckt vid observervationen på fyndplatsen. Finns sannolikt fler plantor här.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5560,32 +5677,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5603,42 +5701,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129788690</v>
+        <v>129788720</v>
       </c>
       <c r="B39" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5650,10 +5756,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>472088</v>
+        <v>472282</v>
       </c>
       <c r="R39" t="n">
-        <v>7028985</v>
+        <v>7028952</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5690,7 +5796,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska och äldre, i riklig mängd på en gran vid hyggeskanten.</t>
+          <t>Minst 280 plantor och 2 vinterståndare inom ca 2 m2 yta i granskog.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5699,32 +5805,13 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5742,42 +5829,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129788700</v>
+        <v>129788721</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5789,10 +5884,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>472091</v>
+        <v>472388</v>
       </c>
       <c r="R40" t="n">
-        <v>7028924</v>
+        <v>7028829</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5829,7 +5924,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 30 plantor och 3 vinterståndare inom ca 1 m2 yta i granskog på fuktig /blöt mark med synligt markvatten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5838,32 +5933,13 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Gransumpskog</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5881,10 +5957,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129788715</v>
+        <v>129788722</v>
       </c>
       <c r="B41" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5911,7 +5987,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5936,10 +6012,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>472454</v>
+        <v>472240</v>
       </c>
       <c r="R41" t="n">
-        <v>7028715</v>
+        <v>7028927</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5976,7 +6052,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 16 plantor inom ca 1,5 m2 yta i äldre barrblandskog.</t>
+          <t>Minst 80 plantor och 7 vinterståndare inom ca 2 m2 yta i en kort sluttning.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6009,42 +6085,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129788684</v>
+        <v>129788723</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6056,10 +6140,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>472106</v>
+        <v>472131</v>
       </c>
       <c r="R42" t="n">
-        <v>7028852</v>
+        <v>7028919</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6096,7 +6180,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), äldre, på en gran.</t>
+          <t>Minst 5 plantor inom ca 1 m2 yta i äldre granskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6105,32 +6189,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6148,10 +6213,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129788713</v>
+        <v>129788724</v>
       </c>
       <c r="B43" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6178,7 +6243,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6203,10 +6268,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>472513</v>
+        <v>472142</v>
       </c>
       <c r="R43" t="n">
-        <v>7028648</v>
+        <v>7028942</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6243,7 +6308,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 30 plantor inom ca 1 m2 yta.</t>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6276,65 +6341,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129788718</v>
+        <v>129788706</v>
       </c>
       <c r="B44" t="n">
-        <v>98831</v>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>472399</v>
+        <v>472382</v>
       </c>
       <c r="R44" t="n">
-        <v>7028764</v>
+        <v>7028711</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6371,7 +6416,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 46 plantor och 1 vinterståndare inom ca 1 m2 yta i äldre granskog.</t>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6380,14 +6425,8 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6404,57 +6443,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129788695</v>
+        <v>129788707</v>
       </c>
       <c r="B45" t="n">
-        <v>57741</v>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kattuggelflon, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>472086</v>
+        <v>472260</v>
       </c>
       <c r="R45" t="n">
-        <v>7028963</v>
+        <v>7028803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6489,11 +6516,6 @@
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack (savhack), äldre, i riklig mängd på en gran vid hyggeskanten.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -6502,31 +6524,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6540,134 +6537,6 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>129788717</v>
-      </c>
-      <c r="B46" t="n">
-        <v>98831</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Kattuggelflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>472404</v>
-      </c>
-      <c r="R46" t="n">
-        <v>7028751</v>
-      </c>
-      <c r="S46" t="n">
-        <v>10</v>
-      </c>
-      <c r="T46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 18 plantor inom ca 1 m2 yta i äldre storvuxen granskog.</t>
-        </is>
-      </c>
-      <c r="AD46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50411-2025 artfynd.xlsx
+++ b/artfynd/A 50411-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -807,6 +812,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -942,6 +952,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788673</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1073,6 +1088,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788726</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1204,6 +1224,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788727</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1343,6 +1368,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788681</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1482,6 +1512,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788682</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1621,6 +1656,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788683</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1760,6 +1800,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1899,6 +1944,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788685</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2038,6 +2088,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788686</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2177,6 +2232,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788687</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2316,6 +2376,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788688</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2455,6 +2520,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788689</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2594,6 +2664,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788690</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2733,6 +2808,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788691</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2872,6 +2952,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788692</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3011,6 +3096,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788693</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3150,6 +3240,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788694</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3289,6 +3384,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788695</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3428,6 +3528,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788696</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3567,6 +3672,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788697</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3706,6 +3816,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788698</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3845,6 +3960,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788699</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3984,6 +4104,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788700</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4123,6 +4248,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788701</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4262,6 +4392,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788702</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4401,6 +4536,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788703</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4540,6 +4680,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788704</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4679,6 +4824,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788705</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4802,6 +4952,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788709</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4930,6 +5085,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788713</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5058,6 +5218,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788714</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5186,6 +5351,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788715</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5314,6 +5484,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788716</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5442,6 +5617,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788717</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5570,6 +5750,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788718</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5698,6 +5883,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788719</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5826,6 +6016,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788720</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5954,6 +6149,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788721</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6082,6 +6282,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788722</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6210,6 +6415,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788723</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6338,6 +6548,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788724</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6440,6 +6655,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788706</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6537,8 +6757,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129788707</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>